--- a/basedatos_partidas/salida/descompuestos/07.04.01.100.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.01.100.xlsx
@@ -584,10 +584,10 @@
         <v>0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>44.08</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="15">
@@ -821,10 +821,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>58.22</v>
+        <v>58.54</v>
       </c>
       <c r="H24" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="25">
@@ -840,7 +840,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>58.8</v>
+        <v>59.13</v>
       </c>
     </row>
   </sheetData>
